--- a/artfynd/A 36101-2022 artfynd.xlsx
+++ b/artfynd/A 36101-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36101-2022 artfynd.xlsx
+++ b/artfynd/A 36101-2022 artfynd.xlsx
@@ -2943,10 +2943,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117863149</v>
+        <v>117863151</v>
       </c>
       <c r="B22" t="n">
-        <v>104929</v>
+        <v>78480</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2955,25 +2955,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502091</v>
+        <v>501959</v>
       </c>
       <c r="R22" t="n">
-        <v>6923432</v>
+        <v>6923361</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117863151</v>
+        <v>117863149</v>
       </c>
       <c r="B23" t="n">
-        <v>78480</v>
+        <v>104929</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3057,25 +3057,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>501959</v>
+        <v>502091</v>
       </c>
       <c r="R23" t="n">
-        <v>6923361</v>
+        <v>6923432</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117863134</v>
+        <v>117863133</v>
       </c>
       <c r="B26" t="n">
-        <v>78217</v>
+        <v>78506</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3363,25 +3363,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>501801</v>
+        <v>502057</v>
       </c>
       <c r="R26" t="n">
-        <v>6923584</v>
+        <v>6923537</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117863133</v>
+        <v>117863134</v>
       </c>
       <c r="B27" t="n">
-        <v>78506</v>
+        <v>78217</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3465,25 +3465,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>502057</v>
+        <v>501801</v>
       </c>
       <c r="R27" t="n">
-        <v>6923537</v>
+        <v>6923584</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 36101-2022 artfynd.xlsx
+++ b/artfynd/A 36101-2022 artfynd.xlsx
@@ -2943,10 +2943,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117863151</v>
+        <v>117863144</v>
       </c>
       <c r="B22" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2959,21 +2959,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>501959</v>
+        <v>502092</v>
       </c>
       <c r="R22" t="n">
-        <v>6923361</v>
+        <v>6923443</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117863149</v>
+        <v>117863141</v>
       </c>
       <c r="B23" t="n">
-        <v>104929</v>
+        <v>78217</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3057,25 +3057,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502091</v>
+        <v>502075</v>
       </c>
       <c r="R23" t="n">
-        <v>6923432</v>
+        <v>6923421</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3147,10 +3147,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117863153</v>
+        <v>117863151</v>
       </c>
       <c r="B24" t="n">
-        <v>91772</v>
+        <v>78480</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3159,25 +3159,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>502067</v>
+        <v>501959</v>
       </c>
       <c r="R24" t="n">
-        <v>6923577</v>
+        <v>6923361</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117863131</v>
+        <v>117863130</v>
       </c>
       <c r="B25" t="n">
-        <v>79562</v>
+        <v>79590</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3261,25 +3261,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117863133</v>
+        <v>117863138</v>
       </c>
       <c r="B26" t="n">
-        <v>78506</v>
+        <v>78217</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3363,25 +3363,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>502057</v>
+        <v>502081</v>
       </c>
       <c r="R26" t="n">
-        <v>6923537</v>
+        <v>6923476</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117863134</v>
+        <v>117857117</v>
       </c>
       <c r="B27" t="n">
-        <v>78217</v>
+        <v>91772</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3465,38 +3465,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fågelvik, Mpd</t>
+          <t>Långtjärnen (Långtjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>501801</v>
+        <v>501933</v>
       </c>
       <c r="R27" t="n">
-        <v>6923584</v>
+        <v>6923362</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3526,9 +3526,19 @@
           <t>2024-06-18</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3543,22 +3553,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117863145</v>
+        <v>117863143</v>
       </c>
       <c r="B28" t="n">
-        <v>78216</v>
+        <v>79561</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3571,21 +3581,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3595,10 +3605,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>501988</v>
+        <v>501914</v>
       </c>
       <c r="R28" t="n">
-        <v>6923363</v>
+        <v>6923365</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3657,10 +3667,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117863143</v>
+        <v>117863129</v>
       </c>
       <c r="B29" t="n">
-        <v>79561</v>
+        <v>57440</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3673,21 +3683,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3697,10 +3707,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>501914</v>
+        <v>501917</v>
       </c>
       <c r="R29" t="n">
-        <v>6923365</v>
+        <v>6923368</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3735,6 +3745,11 @@
           <t>2024-06-18</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3752,14 +3767,14 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117863155</v>
+        <v>117863154</v>
       </c>
       <c r="B30" t="n">
         <v>91772</v>
@@ -3799,10 +3814,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>501917</v>
+        <v>502039</v>
       </c>
       <c r="R30" t="n">
-        <v>6923368</v>
+        <v>6923372</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3861,10 +3876,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117857104</v>
+        <v>117863145</v>
       </c>
       <c r="B31" t="n">
-        <v>79561</v>
+        <v>78216</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3877,34 +3892,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långtjärnen (Långtjärnen), Mpd</t>
+          <t>Fågelvik, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>501933</v>
+        <v>501988</v>
       </c>
       <c r="R31" t="n">
-        <v>6923355</v>
+        <v>6923363</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3934,24 +3949,9 @@
           <t>2024-06-18</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-06-18</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3966,22 +3966,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117863144</v>
+        <v>117863134</v>
       </c>
       <c r="B32" t="n">
-        <v>78216</v>
+        <v>78217</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3994,21 +3994,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>502092</v>
+        <v>501801</v>
       </c>
       <c r="R32" t="n">
-        <v>6923443</v>
+        <v>6923584</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4080,10 +4080,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117863138</v>
+        <v>117863131</v>
       </c>
       <c r="B33" t="n">
-        <v>78217</v>
+        <v>79562</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>502081</v>
+        <v>501914</v>
       </c>
       <c r="R33" t="n">
-        <v>6923476</v>
+        <v>6923365</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4182,10 +4182,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117863130</v>
+        <v>117857104</v>
       </c>
       <c r="B34" t="n">
-        <v>79590</v>
+        <v>79561</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4194,38 +4194,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fågelvik, Mpd</t>
+          <t>Långtjärnen (Långtjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>501914</v>
+        <v>501933</v>
       </c>
       <c r="R34" t="n">
-        <v>6923365</v>
+        <v>6923355</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4255,9 +4255,24 @@
           <t>2024-06-18</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4272,19 +4287,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117863139</v>
+        <v>117863140</v>
       </c>
       <c r="B35" t="n">
         <v>78217</v>
@@ -4324,10 +4339,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>502092</v>
+        <v>502073</v>
       </c>
       <c r="R35" t="n">
-        <v>6923443</v>
+        <v>6923407</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4386,10 +4401,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117863129</v>
+        <v>117863153</v>
       </c>
       <c r="B36" t="n">
-        <v>57440</v>
+        <v>91772</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4398,25 +4413,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4426,10 +4441,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>501917</v>
+        <v>502067</v>
       </c>
       <c r="R36" t="n">
-        <v>6923368</v>
+        <v>6923577</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4464,11 +4479,6 @@
           <t>2024-06-18</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Sång</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4486,17 +4496,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117863140</v>
+        <v>117863127</v>
       </c>
       <c r="B37" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4509,21 +4519,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4533,10 +4543,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>502073</v>
+        <v>502092</v>
       </c>
       <c r="R37" t="n">
-        <v>6923407</v>
+        <v>6923443</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4588,17 +4598,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117863154</v>
+        <v>117858004</v>
       </c>
       <c r="B38" t="n">
-        <v>91772</v>
+        <v>58102</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4611,34 +4621,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>208245</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Fågelvik, Mpd</t>
+          <t>Långtjärnen (Långtjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502039</v>
+        <v>502079</v>
       </c>
       <c r="R38" t="n">
-        <v>6923372</v>
+        <v>6923452</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4668,9 +4678,19 @@
           <t>2024-06-18</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4685,22 +4705,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117863127</v>
+        <v>117863133</v>
       </c>
       <c r="B39" t="n">
-        <v>79098</v>
+        <v>78506</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4709,25 +4729,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4737,10 +4757,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>502092</v>
+        <v>502057</v>
       </c>
       <c r="R39" t="n">
-        <v>6923443</v>
+        <v>6923537</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4792,17 +4812,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117858004</v>
+        <v>117863155</v>
       </c>
       <c r="B40" t="n">
-        <v>58102</v>
+        <v>91772</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4815,34 +4835,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>208245</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Långtjärnen (Långtjärnen), Mpd</t>
+          <t>Fågelvik, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>502079</v>
+        <v>501917</v>
       </c>
       <c r="R40" t="n">
-        <v>6923452</v>
+        <v>6923368</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4872,19 +4892,9 @@
           <t>2024-06-18</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-06-18</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4899,22 +4909,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117863141</v>
+        <v>117863149</v>
       </c>
       <c r="B41" t="n">
-        <v>78217</v>
+        <v>104929</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4923,25 +4933,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>221144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4951,10 +4961,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>502075</v>
+        <v>502091</v>
       </c>
       <c r="R41" t="n">
-        <v>6923421</v>
+        <v>6923432</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5013,10 +5023,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117857117</v>
+        <v>117863139</v>
       </c>
       <c r="B42" t="n">
-        <v>91772</v>
+        <v>78217</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5025,38 +5035,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Långtjärnen (Långtjärnen), Mpd</t>
+          <t>Fågelvik, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>501933</v>
+        <v>502092</v>
       </c>
       <c r="R42" t="n">
-        <v>6923362</v>
+        <v>6923443</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5086,19 +5096,9 @@
           <t>2024-06-18</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-06-18</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5113,12 +5113,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117883973</v>
+        <v>117883976</v>
       </c>
       <c r="B44" t="n">
-        <v>90648</v>
+        <v>77412</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5239,25 +5239,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1503</v>
+        <v>6487</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>501921</v>
+        <v>502077</v>
       </c>
       <c r="R44" t="n">
-        <v>6923352</v>
+        <v>6923566</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
+          <t>Linda Spjut, Amanda Tas, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5424,17 +5424,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
+          <t>Linda Spjut, Amanda Tas, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117883976</v>
+        <v>117883973</v>
       </c>
       <c r="B46" t="n">
-        <v>77412</v>
+        <v>90648</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5443,25 +5443,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6487</v>
+        <v>1503</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>502077</v>
+        <v>501921</v>
       </c>
       <c r="R46" t="n">
-        <v>6923566</v>
+        <v>6923352</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Linda Spjut, Marielle Löthman, Amanda Tas</t>
+          <t>Linda Spjut, Amanda Tas, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>

--- a/artfynd/A 36101-2022 artfynd.xlsx
+++ b/artfynd/A 36101-2022 artfynd.xlsx
@@ -2943,10 +2943,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117863144</v>
+        <v>117863153</v>
       </c>
       <c r="B22" t="n">
-        <v>78216</v>
+        <v>91774</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2955,25 +2955,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502092</v>
+        <v>502067</v>
       </c>
       <c r="R22" t="n">
-        <v>6923443</v>
+        <v>6923577</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117863141</v>
+        <v>117863133</v>
       </c>
       <c r="B23" t="n">
-        <v>78217</v>
+        <v>78508</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3057,25 +3057,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502075</v>
+        <v>502057</v>
       </c>
       <c r="R23" t="n">
-        <v>6923421</v>
+        <v>6923537</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3147,10 +3147,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117863151</v>
+        <v>117863145</v>
       </c>
       <c r="B24" t="n">
-        <v>78480</v>
+        <v>78218</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3163,21 +3163,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>501959</v>
+        <v>501988</v>
       </c>
       <c r="R24" t="n">
-        <v>6923361</v>
+        <v>6923363</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117863130</v>
+        <v>117863127</v>
       </c>
       <c r="B25" t="n">
-        <v>79590</v>
+        <v>79100</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3261,25 +3261,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>501914</v>
+        <v>502092</v>
       </c>
       <c r="R25" t="n">
-        <v>6923365</v>
+        <v>6923443</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117863138</v>
+        <v>117863139</v>
       </c>
       <c r="B26" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>502081</v>
+        <v>502092</v>
       </c>
       <c r="R26" t="n">
-        <v>6923476</v>
+        <v>6923443</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117857117</v>
+        <v>117863149</v>
       </c>
       <c r="B27" t="n">
-        <v>91772</v>
+        <v>104931</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3469,34 +3469,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långtjärnen (Långtjärnen), Mpd</t>
+          <t>Fågelvik, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>501933</v>
+        <v>502091</v>
       </c>
       <c r="R27" t="n">
-        <v>6923362</v>
+        <v>6923432</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3526,19 +3526,9 @@
           <t>2024-06-18</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-06-18</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3553,22 +3543,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117863143</v>
+        <v>117863137</v>
       </c>
       <c r="B28" t="n">
-        <v>79561</v>
+        <v>78219</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3581,21 +3571,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3605,10 +3595,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>501914</v>
+        <v>502067</v>
       </c>
       <c r="R28" t="n">
-        <v>6923365</v>
+        <v>6923577</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3667,10 +3657,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117863129</v>
+        <v>117863138</v>
       </c>
       <c r="B29" t="n">
-        <v>57440</v>
+        <v>78219</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3683,21 +3673,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3707,10 +3697,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>501917</v>
+        <v>502081</v>
       </c>
       <c r="R29" t="n">
-        <v>6923368</v>
+        <v>6923476</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3745,11 +3735,6 @@
           <t>2024-06-18</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Sång</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3767,7 +3752,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3777,7 +3762,7 @@
         <v>117863154</v>
       </c>
       <c r="B30" t="n">
-        <v>91772</v>
+        <v>91774</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3876,10 +3861,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117863145</v>
+        <v>117863144</v>
       </c>
       <c r="B31" t="n">
-        <v>78216</v>
+        <v>78218</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3916,10 +3901,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>501988</v>
+        <v>502092</v>
       </c>
       <c r="R31" t="n">
-        <v>6923363</v>
+        <v>6923443</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3978,10 +3963,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117863134</v>
+        <v>117863143</v>
       </c>
       <c r="B32" t="n">
-        <v>78217</v>
+        <v>79563</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3994,21 +3979,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4018,10 +4003,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>501801</v>
+        <v>501914</v>
       </c>
       <c r="R32" t="n">
-        <v>6923584</v>
+        <v>6923365</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4080,10 +4065,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117863131</v>
+        <v>117863134</v>
       </c>
       <c r="B33" t="n">
-        <v>79562</v>
+        <v>78219</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4096,21 +4081,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4120,10 +4105,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>501914</v>
+        <v>501801</v>
       </c>
       <c r="R33" t="n">
-        <v>6923365</v>
+        <v>6923584</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4185,7 +4170,7 @@
         <v>117857104</v>
       </c>
       <c r="B34" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4299,10 +4284,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117863140</v>
+        <v>117863130</v>
       </c>
       <c r="B35" t="n">
-        <v>78217</v>
+        <v>79592</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4311,25 +4296,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4339,10 +4324,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>502073</v>
+        <v>501914</v>
       </c>
       <c r="R35" t="n">
-        <v>6923407</v>
+        <v>6923365</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4401,10 +4386,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117863153</v>
+        <v>117863140</v>
       </c>
       <c r="B36" t="n">
-        <v>91772</v>
+        <v>78219</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4413,25 +4398,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4441,10 +4426,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>502067</v>
+        <v>502073</v>
       </c>
       <c r="R36" t="n">
-        <v>6923577</v>
+        <v>6923407</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4503,10 +4488,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117863127</v>
+        <v>117857117</v>
       </c>
       <c r="B37" t="n">
-        <v>79098</v>
+        <v>91774</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4515,38 +4500,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fågelvik, Mpd</t>
+          <t>Långtjärnen (Långtjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>502092</v>
+        <v>501933</v>
       </c>
       <c r="R37" t="n">
-        <v>6923443</v>
+        <v>6923362</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4576,9 +4561,19 @@
           <t>2024-06-18</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4593,22 +4588,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117858004</v>
+        <v>117863131</v>
       </c>
       <c r="B38" t="n">
-        <v>58102</v>
+        <v>79564</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4617,38 +4612,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>208245</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Långtjärnen (Långtjärnen), Mpd</t>
+          <t>Fågelvik, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502079</v>
+        <v>501914</v>
       </c>
       <c r="R38" t="n">
-        <v>6923452</v>
+        <v>6923365</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4678,19 +4673,9 @@
           <t>2024-06-18</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-06-18</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>12:34</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4705,22 +4690,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117863133</v>
+        <v>117863129</v>
       </c>
       <c r="B39" t="n">
-        <v>78506</v>
+        <v>57441</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4729,25 +4714,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6434</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4757,10 +4742,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>502057</v>
+        <v>501917</v>
       </c>
       <c r="R39" t="n">
-        <v>6923537</v>
+        <v>6923368</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4795,6 +4780,11 @@
           <t>2024-06-18</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4812,7 +4802,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4822,7 +4812,7 @@
         <v>117863155</v>
       </c>
       <c r="B40" t="n">
-        <v>91772</v>
+        <v>91774</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4921,10 +4911,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117863149</v>
+        <v>117863151</v>
       </c>
       <c r="B41" t="n">
-        <v>104929</v>
+        <v>78482</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4933,25 +4923,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4961,10 +4951,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>502091</v>
+        <v>501959</v>
       </c>
       <c r="R41" t="n">
-        <v>6923432</v>
+        <v>6923361</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5023,10 +5013,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117863139</v>
+        <v>117858004</v>
       </c>
       <c r="B42" t="n">
-        <v>78217</v>
+        <v>58103</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5035,38 +5025,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>208245</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fågelvik, Mpd</t>
+          <t>Långtjärnen (Långtjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>502092</v>
+        <v>502079</v>
       </c>
       <c r="R42" t="n">
-        <v>6923443</v>
+        <v>6923452</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5096,9 +5086,19 @@
           <t>2024-06-18</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5113,22 +5113,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Amanda Tas, Marielle Löthman, Linda Spjut</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117863137</v>
+        <v>117863141</v>
       </c>
       <c r="B43" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>502067</v>
+        <v>502075</v>
       </c>
       <c r="R43" t="n">
-        <v>6923577</v>
+        <v>6923421</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117883976</v>
+        <v>117883973</v>
       </c>
       <c r="B44" t="n">
-        <v>77412</v>
+        <v>90650</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5239,25 +5239,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6487</v>
+        <v>1503</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>502077</v>
+        <v>501921</v>
       </c>
       <c r="R44" t="n">
-        <v>6923566</v>
+        <v>6923352</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5329,10 +5329,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117883963</v>
+        <v>117883976</v>
       </c>
       <c r="B45" t="n">
-        <v>90425</v>
+        <v>77414</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5345,21 +5345,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3242</v>
+        <v>6487</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5369,10 +5369,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>502025</v>
+        <v>502077</v>
       </c>
       <c r="R45" t="n">
-        <v>6923387</v>
+        <v>6923566</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5431,10 +5431,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117883973</v>
+        <v>117883963</v>
       </c>
       <c r="B46" t="n">
-        <v>90648</v>
+        <v>90427</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5443,25 +5443,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1503</v>
+        <v>3242</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>501921</v>
+        <v>502025</v>
       </c>
       <c r="R46" t="n">
-        <v>6923352</v>
+        <v>6923387</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
